--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_49.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_49.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SelfConfidence</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>Perfectionism</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.473751469295161</v>
+        <v>1.551267345357723</v>
       </c>
       <c r="C2">
-        <v>-0.2149109467403755</v>
+        <v>-0.3736183071764088</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.3893804472982652</v>
+        <v>-0.9381703500983387</v>
       </c>
       <c r="C3">
-        <v>-0.05324898497323605</v>
+        <v>0.8732054087616655</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.8003709674395824</v>
+        <v>0.2255153445172484</v>
       </c>
       <c r="C4">
-        <v>-0.7772964876300107</v>
+        <v>-0.8850156565890266</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.40412921479819</v>
+        <v>1.809814206826715</v>
       </c>
       <c r="C5">
-        <v>-1.629609086680532</v>
+        <v>-1.466901091173537</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.7970626507587983</v>
+        <v>0.01019421507711463</v>
       </c>
       <c r="C6">
-        <v>0.590350843420264</v>
+        <v>-0.6786874607356685</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.3129030937957893</v>
+        <v>0.8309236393394615</v>
       </c>
       <c r="C7">
-        <v>0.1010381172566611</v>
+        <v>-0.0179546915986688</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.04788233548985749</v>
+        <v>0.3618082854285201</v>
       </c>
       <c r="C8">
-        <v>0.7541588027091375</v>
+        <v>0.6311226085375689</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.9351499986287664</v>
+        <v>0.2091471627514322</v>
       </c>
       <c r="C9">
-        <v>-0.3497117040105743</v>
+        <v>-0.262675480487623</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.07206075372042935</v>
+        <v>1.558486142610286</v>
       </c>
       <c r="C10">
-        <v>0.6963083715915619</v>
+        <v>0.6165468372843371</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.537496080377384</v>
+        <v>-0.4959342982926359</v>
       </c>
       <c r="C11">
-        <v>0.2107204658239055</v>
+        <v>-0.1349045523868672</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.375354482089149</v>
+        <v>0.05339021513572841</v>
       </c>
       <c r="C12">
-        <v>-1.43777642473911</v>
+        <v>0.6861028198431803</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-1.853134222570227</v>
+        <v>0.3007239523205259</v>
       </c>
       <c r="C13">
-        <v>-0.4745848072969802</v>
+        <v>-0.9395000668722348</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.243046162316809</v>
+        <v>0.7706913763221031</v>
       </c>
       <c r="C14">
-        <v>0.3654092774433083</v>
+        <v>-2.217180379263482</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.7242364665852795</v>
+        <v>-1.273858558267444</v>
       </c>
       <c r="C15">
-        <v>-0.1997775649732403</v>
+        <v>1.57755499940858</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.8392819783256713</v>
+        <v>-0.07790846711943689</v>
       </c>
       <c r="C16">
-        <v>0.577790195970611</v>
+        <v>-1.497680589045091</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.246455850309691</v>
+        <v>-1.119028063629004</v>
       </c>
       <c r="C17">
-        <v>0.3260365356002188</v>
+        <v>2.158526458255751</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.6072463042384691</v>
+        <v>-2.484606651397967</v>
       </c>
       <c r="C18">
-        <v>-0.8702158928755475</v>
+        <v>2.424103834609925</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.9682196625109927</v>
+        <v>-0.3831688744958034</v>
       </c>
       <c r="C19">
-        <v>0.8683186129157701</v>
+        <v>-0.3642973212613586</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.1069363120657946</v>
+        <v>-0.9843402050825059</v>
       </c>
       <c r="C20">
-        <v>-0.5261110932146313</v>
+        <v>-0.3819165435179963</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.3570827020644142</v>
+        <v>-0.5191196632339031</v>
       </c>
       <c r="C21">
-        <v>-1.031603547111405</v>
+        <v>-0.008288745272789305</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.4491707931275838</v>
+        <v>-1.428011571200932</v>
       </c>
       <c r="C22">
-        <v>-0.5096675084966206</v>
+        <v>1.005771564347084</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.594720444423723</v>
+        <v>0.03880301820041211</v>
       </c>
       <c r="C23">
-        <v>-0.8819580335602161</v>
+        <v>0.7092563902829464</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.8429745219667893</v>
+        <v>-0.8426096492787597</v>
       </c>
       <c r="C24">
-        <v>1.070146007158831</v>
+        <v>1.025883301097719</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.9338050159510766</v>
+        <v>0.3766857109240375</v>
       </c>
       <c r="C25">
-        <v>-0.3088332518219896</v>
+        <v>1.563195862858856</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.8213622818369816</v>
+        <v>-1.778221627873788</v>
       </c>
       <c r="C26">
-        <v>-1.127988383372271</v>
+        <v>0.6141449501389742</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.272073494076571</v>
+        <v>-0.2465947255038141</v>
       </c>
       <c r="C27">
-        <v>1.680899767270746</v>
+        <v>0.1899809403292804</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.6559920147403282</v>
+        <v>0.6787870772343675</v>
       </c>
       <c r="C28">
-        <v>-1.34095775072186</v>
+        <v>-0.4366804987476167</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.388969668469033</v>
+        <v>-0.1046179433514904</v>
       </c>
       <c r="C29">
-        <v>0.6914981352222315</v>
+        <v>-1.615727251486015</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.1018780574094565</v>
+        <v>0.195866902671627</v>
       </c>
       <c r="C30">
-        <v>-0.2097867451910245</v>
+        <v>-0.2179499023269613</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.7788937316105135</v>
+        <v>-1.449226866914604</v>
       </c>
       <c r="C31">
-        <v>-0.7254164254716192</v>
+        <v>1.034666652344987</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.7175209072072701</v>
+        <v>1.170506360297672</v>
       </c>
       <c r="C32">
-        <v>1.254303551206229</v>
+        <v>-0.8303491922446065</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-1.21382691239862</v>
+        <v>0.8754355205717702</v>
       </c>
       <c r="C33">
-        <v>0.09817474186347042</v>
+        <v>0.1993033829697745</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.5001357240098114</v>
+        <v>0.5447588602633517</v>
       </c>
       <c r="C34">
-        <v>-0.1159696091036952</v>
+        <v>1.223117408295545</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-3.018760678496655</v>
+        <v>-0.1189095069867767</v>
       </c>
       <c r="C35">
-        <v>1.784808861488485</v>
+        <v>1.429749536529079</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.4417539184665328</v>
+        <v>-0.9401489120177036</v>
       </c>
       <c r="C36">
-        <v>-0.4594271136993957</v>
+        <v>1.165907796134591</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.644991139056403</v>
+        <v>-0.2092305290692572</v>
       </c>
       <c r="C37">
-        <v>1.790981308149843</v>
+        <v>1.478104696489731</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-2.005649060336538</v>
+        <v>-1.300378167877568</v>
       </c>
       <c r="C38">
-        <v>1.44441787878609</v>
+        <v>0.3272975163521051</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.1002641622614985</v>
+        <v>-0.1221374235826043</v>
       </c>
       <c r="C39">
-        <v>0.2102335222195187</v>
+        <v>0.4078700164065259</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.738738768391089</v>
+        <v>1.009641377420184</v>
       </c>
       <c r="C40">
-        <v>0.2367426717790642</v>
+        <v>-0.4239533269135037</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.1034988959527454</v>
+        <v>-0.6056126029499668</v>
       </c>
       <c r="C41">
-        <v>-0.8644131918369026</v>
+        <v>0.7726481737839789</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.3237345403516511</v>
+        <v>0.1064556265758107</v>
       </c>
       <c r="C42">
-        <v>0.545431383865586</v>
+        <v>-0.1602596337378568</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.6332933463758905</v>
+        <v>1.933609858925564</v>
       </c>
       <c r="C43">
-        <v>-0.3377646021042335</v>
+        <v>0.4234064513581367</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.655433121510867</v>
+        <v>0.4729298860235767</v>
       </c>
       <c r="C44">
-        <v>2.022578978352917</v>
+        <v>0.190470014352605</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.6130893976156483</v>
+        <v>1.12946210409782</v>
       </c>
       <c r="C45">
-        <v>0.005267461592887213</v>
+        <v>0.1998579732472968</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.556666021685108</v>
+        <v>1.379476928641362</v>
       </c>
       <c r="C46">
-        <v>-0.1219775183553823</v>
+        <v>0.1045868977631821</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.5420007300707733</v>
+        <v>0.5022875118433383</v>
       </c>
       <c r="C47">
-        <v>0.6231988719519629</v>
+        <v>0.0855513513067778</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.218031473397319</v>
+        <v>-2.670909155564702</v>
       </c>
       <c r="C48">
-        <v>-0.1175320337496659</v>
+        <v>1.097555401286327</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.3427775998958639</v>
+        <v>-0.2592019621023365</v>
       </c>
       <c r="C49">
-        <v>-0.1008778157404058</v>
+        <v>-0.1336261956412884</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.61049437734289</v>
+        <v>-0.9944881331493131</v>
       </c>
       <c r="C50">
-        <v>-0.9252817320744713</v>
+        <v>0.6515122772129365</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.896093450704918</v>
+        <v>0.3866456836493173</v>
       </c>
       <c r="C51">
-        <v>-1.802275595923634</v>
+        <v>-0.188141246846955</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.3797806906212255</v>
+      </c>
+      <c r="C52">
+        <v>-1.748771966847328</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-1.068596814271543</v>
+      </c>
+      <c r="C53">
+        <v>0.2526233304429261</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-1.124037128764361</v>
+      </c>
+      <c r="C54">
+        <v>-0.1537893173881195</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>-1.60439820298212</v>
+      </c>
+      <c r="C55">
+        <v>1.731998263927587</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.5927889338559064</v>
+      </c>
+      <c r="C56">
+        <v>1.771464562057586</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-1.310162965909651</v>
+      </c>
+      <c r="C57">
+        <v>1.236875912450328</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-0.9525568440929257</v>
+      </c>
+      <c r="C58">
+        <v>0.1694226009138776</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>1.517051679494349</v>
+      </c>
+      <c r="C59">
+        <v>-1.162894156237358</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>1.676477687662373</v>
+      </c>
+      <c r="C60">
+        <v>-0.2222132907108961</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>-0.2550041167605978</v>
+      </c>
+      <c r="C61">
+        <v>1.124864084973856</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-0.2927128781961115</v>
+      </c>
+      <c r="C62">
+        <v>0.2498991319938215</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>1.355476450754264</v>
+      </c>
+      <c r="C63">
+        <v>-0.3800498738124108</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>0.6194369607922062</v>
+      </c>
+      <c r="C64">
+        <v>-0.01223129130833428</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.8368937254049021</v>
+      </c>
+      <c r="C65">
+        <v>-1.007120157803635</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-0.00713118102142529</v>
+      </c>
+      <c r="C66">
+        <v>0.8572071393887981</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>-1.512292631216511</v>
+      </c>
+      <c r="C67">
+        <v>-0.5492718202534755</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>2.151157932966187</v>
+      </c>
+      <c r="C68">
+        <v>-0.3853948400478135</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>0.4754721837175742</v>
+      </c>
+      <c r="C69">
+        <v>-0.4484776993631876</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.03722472940652501</v>
+      </c>
+      <c r="C70">
+        <v>-0.9307952629478311</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-0.08616529440379644</v>
+      </c>
+      <c r="C71">
+        <v>-0.596745921044357</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>1.142740770733672</v>
+      </c>
+      <c r="C72">
+        <v>-0.5255024827812914</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-0.3384391448568355</v>
+      </c>
+      <c r="C73">
+        <v>-0.09937166376692277</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.4831901097073396</v>
+      </c>
+      <c r="C74">
+        <v>-0.3526965687845965</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>-0.4053378991576345</v>
+      </c>
+      <c r="C75">
+        <v>0.26643647431671</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>1.80537677430666</v>
+      </c>
+      <c r="C76">
+        <v>-1.556270689251838</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>1.544676807087125</v>
+      </c>
+      <c r="C77">
+        <v>-1.061276417169412</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>1.173674504380789</v>
+      </c>
+      <c r="C78">
+        <v>0.1859889732053939</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-0.1487290677570428</v>
+      </c>
+      <c r="C79">
+        <v>0.3827699554199534</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-0.5320710416481884</v>
+      </c>
+      <c r="C80">
+        <v>-1.547241132263319</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>0.4965824178768973</v>
+      </c>
+      <c r="C81">
+        <v>0.9399264437818959</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>-0.1255318957952967</v>
+      </c>
+      <c r="C82">
+        <v>-0.03552246727305249</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>-0.5221354929148396</v>
+      </c>
+      <c r="C83">
+        <v>0.9913081735640991</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-1.69207396231639</v>
+      </c>
+      <c r="C84">
+        <v>0.1952073748616434</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>0.1753630008119319</v>
+      </c>
+      <c r="C85">
+        <v>-1.572227195173787</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>0.1712663220372481</v>
+      </c>
+      <c r="C86">
+        <v>-0.2624810588680489</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-1.160236528348096</v>
+      </c>
+      <c r="C87">
+        <v>0.3791493603461345</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>0.9271474092665639</v>
+      </c>
+      <c r="C88">
+        <v>0.9486551210993648</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>-0.5319970433818285</v>
+      </c>
+      <c r="C89">
+        <v>1.492698893987476</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>-0.3492799893243029</v>
+      </c>
+      <c r="C90">
+        <v>1.13821388347821</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-2.575111367765472</v>
+      </c>
+      <c r="C91">
+        <v>1.238811758585929</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>0.01492214390018774</v>
+      </c>
+      <c r="C92">
+        <v>-0.03658144732295131</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>1.127146761423558</v>
+      </c>
+      <c r="C93">
+        <v>0.3464967397893309</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>0.6651228505502654</v>
+      </c>
+      <c r="C94">
+        <v>-1.392103790781847</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-0.3154796310373835</v>
+      </c>
+      <c r="C95">
+        <v>1.6107459054177</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>-0.9334420195786829</v>
+      </c>
+      <c r="C96">
+        <v>0.6432762272726669</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>-0.5687872541508292</v>
+      </c>
+      <c r="C97">
+        <v>1.540543212077645</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>1.266226424444338</v>
+      </c>
+      <c r="C98">
+        <v>-1.053485497153169</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>-0.1221167578847705</v>
+      </c>
+      <c r="C99">
+        <v>0.2925745915325541</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>1.248504833817709</v>
+      </c>
+      <c r="C100">
+        <v>-1.068885223479189</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>1.976718445178721</v>
+      </c>
+      <c r="C101">
+        <v>0.2912980274479634</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>1.930094257323988</v>
+      </c>
+      <c r="C102">
+        <v>0.8387374648696214</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.721272021167951</v>
+      </c>
+      <c r="C103">
+        <v>-0.2466652905740176</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.9204166893933577</v>
+      </c>
+      <c r="C104">
+        <v>-0.3184441430802101</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.5078171125707944</v>
+      </c>
+      <c r="C105">
+        <v>-0.2541512586484125</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-0.8316944038616576</v>
+      </c>
+      <c r="C106">
+        <v>0.3905680105870981</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.4746413109990091</v>
+      </c>
+      <c r="C107">
+        <v>-0.7510066094781677</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.006771896995330576</v>
+      </c>
+      <c r="C108">
+        <v>-0.6118824550753504</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.1026289916197622</v>
+      </c>
+      <c r="C109">
+        <v>-0.1360454726808386</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-1.050153549850694</v>
+      </c>
+      <c r="C110">
+        <v>1.04841409882841</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1.0872744625281</v>
+      </c>
+      <c r="C111">
+        <v>0.1653020251956233</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-0.9824670332935361</v>
+      </c>
+      <c r="C112">
+        <v>-0.6296113085210976</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.314476782463503</v>
+      </c>
+      <c r="C113">
+        <v>1.453628014191682</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.6637588833311818</v>
+      </c>
+      <c r="C114">
+        <v>0.3516293008789595</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>1.752147380813878</v>
+      </c>
+      <c r="C115">
+        <v>-1.803632414592848</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-0.0572223392868346</v>
+      </c>
+      <c r="C116">
+        <v>0.03850848721538674</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>0.6036378863994604</v>
+      </c>
+      <c r="C117">
+        <v>0.9451462378611361</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.2668889613701359</v>
+      </c>
+      <c r="C118">
+        <v>0.4044075684806543</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-1.457464992347472</v>
+      </c>
+      <c r="C119">
+        <v>0.9866131955103584</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1.131162061343717</v>
+      </c>
+      <c r="C120">
+        <v>0.4527813012172592</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.2765341490400488</v>
+      </c>
+      <c r="C121">
+        <v>-0.690352120741491</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1.434742128901055</v>
+      </c>
+      <c r="C122">
+        <v>-1.61055088422859</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>-0.8656979341242117</v>
+      </c>
+      <c r="C123">
+        <v>0.93755787355542</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.346080437007428</v>
+      </c>
+      <c r="C124">
+        <v>-0.8714112230448396</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.6009416520793897</v>
+      </c>
+      <c r="C125">
+        <v>-0.2228576968421375</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.6793831705965913</v>
+      </c>
+      <c r="C126">
+        <v>-1.128313599864824</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.05517289414408508</v>
+      </c>
+      <c r="C127">
+        <v>-0.2014726095641314</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-1.025790633970871</v>
+      </c>
+      <c r="C128">
+        <v>1.316066214856863</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-0.817834327954149</v>
+      </c>
+      <c r="C129">
+        <v>0.3976200352799232</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.2657947962939645</v>
+      </c>
+      <c r="C130">
+        <v>0.5373315610283222</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.1882230263673302</v>
+      </c>
+      <c r="C131">
+        <v>-0.09152386768230467</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>1.030466756231695</v>
+      </c>
+      <c r="C132">
+        <v>-1.665701020275119</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.4034718194409379</v>
+      </c>
+      <c r="C133">
+        <v>-1.450740718313691</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-0.8423990008727941</v>
+      </c>
+      <c r="C134">
+        <v>1.833385532079217</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.4705672012626698</v>
+      </c>
+      <c r="C135">
+        <v>0.06803365274908166</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.3551829957198612</v>
+      </c>
+      <c r="C136">
+        <v>0.3157639846108664</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.4904527620204626</v>
+      </c>
+      <c r="C137">
+        <v>-0.3550519646181298</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.0698121101244002</v>
+      </c>
+      <c r="C138">
+        <v>0.6388388435034089</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.7187074846945462</v>
+      </c>
+      <c r="C139">
+        <v>-0.3617631305839537</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>1.098368076695306</v>
+      </c>
+      <c r="C140">
+        <v>0.9631272023000923</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>-0.6201076322652485</v>
+      </c>
+      <c r="C141">
+        <v>-0.4658460233740228</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1.598851402635149</v>
+      </c>
+      <c r="C142">
+        <v>-0.4369466286311093</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>1.952537775857432</v>
+      </c>
+      <c r="C143">
+        <v>-0.05375898886173003</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.9323955797213113</v>
+      </c>
+      <c r="C144">
+        <v>0.04133837807737051</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.1410807625951942</v>
+      </c>
+      <c r="C145">
+        <v>-1.889598776097686</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.341217331220908</v>
+      </c>
+      <c r="C146">
+        <v>-1.392724012291761</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.8983128695050887</v>
+      </c>
+      <c r="C147">
+        <v>-0.6510235621405411</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>1.235755048173311</v>
+      </c>
+      <c r="C148">
+        <v>0.2354294050446834</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.999592690948202</v>
+      </c>
+      <c r="C149">
+        <v>-1.424727184861251</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>1.74260276522316</v>
+      </c>
+      <c r="C150">
+        <v>-0.4159993071500934</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-1.036796460885766</v>
+      </c>
+      <c r="C151">
+        <v>0.9148528006069658</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1.314463607101882</v>
+      </c>
+      <c r="C152">
+        <v>-1.939959754799129</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.692415178095492</v>
+      </c>
+      <c r="C153">
+        <v>0.2631371496088023</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-0.3266483720054004</v>
+      </c>
+      <c r="C154">
+        <v>-1.031923731497004</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.4944789452832786</v>
+      </c>
+      <c r="C155">
+        <v>0.9837495897805266</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.1597797654292099</v>
+      </c>
+      <c r="C156">
+        <v>1.295188121216896</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1.375258344270619</v>
+      </c>
+      <c r="C157">
+        <v>-1.291069417644639</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>1.394248421198607</v>
+      </c>
+      <c r="C158">
+        <v>0.689971353467048</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>1.484258308844074</v>
+      </c>
+      <c r="C159">
+        <v>-1.214792056882619</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.7124325271190413</v>
+      </c>
+      <c r="C160">
+        <v>-0.2806196457198644</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-2.361519260002038</v>
+      </c>
+      <c r="C161">
+        <v>0.6282260771413917</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.2831337839137402</v>
+      </c>
+      <c r="C162">
+        <v>-0.3911671028646855</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.07457600110636459</v>
+      </c>
+      <c r="C163">
+        <v>1.877488832426637</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-0.4554446636013234</v>
+      </c>
+      <c r="C164">
+        <v>-0.4568195923977837</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.38056165832932</v>
+      </c>
+      <c r="C165">
+        <v>-0.7691137259048222</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.8445063294286478</v>
+      </c>
+      <c r="C166">
+        <v>1.94447284777881</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-1.362234514493626</v>
+      </c>
+      <c r="C167">
+        <v>0.1418141470861362</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-1.030646311441348</v>
+      </c>
+      <c r="C168">
+        <v>0.1325784989867264</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>0.87657345716622</v>
+      </c>
+      <c r="C169">
+        <v>-1.822044197642625</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.4821244657880941</v>
+      </c>
+      <c r="C170">
+        <v>-1.061242109666523</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.4489431452881982</v>
+      </c>
+      <c r="C171">
+        <v>-0.2361653392715589</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.1304767196720625</v>
+      </c>
+      <c r="C172">
+        <v>-0.4770537314738441</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.2775322439428399</v>
+      </c>
+      <c r="C173">
+        <v>0.6774189046562399</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1.997848712603266</v>
+      </c>
+      <c r="C174">
+        <v>-1.114524230569397</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.0483891819456462</v>
+      </c>
+      <c r="C175">
+        <v>-0.2654687131624651</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>1.44498343316333</v>
+      </c>
+      <c r="C176">
+        <v>-0.005486257658474547</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.02064457004663637</v>
+      </c>
+      <c r="C177">
+        <v>0.379389216832263</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.506113244911336</v>
+      </c>
+      <c r="C178">
+        <v>-0.897776496358345</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>-0.5443692673962601</v>
+      </c>
+      <c r="C179">
+        <v>0.1954941549592838</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.4216534218269036</v>
+      </c>
+      <c r="C180">
+        <v>-0.2928690293947217</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.306747353890981</v>
+      </c>
+      <c r="C181">
+        <v>-1.738032545307648</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.8861860442782359</v>
+      </c>
+      <c r="C182">
+        <v>1.319203617080398</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>2.45867402718165</v>
+      </c>
+      <c r="C183">
+        <v>-1.089034805255139</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.7963919650288867</v>
+      </c>
+      <c r="C184">
+        <v>-0.1988712942184033</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-0.06303201668917946</v>
+      </c>
+      <c r="C185">
+        <v>0.387905157522721</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.48492922264256</v>
+      </c>
+      <c r="C186">
+        <v>-1.425461961417963</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-1.489096676138925</v>
+      </c>
+      <c r="C187">
+        <v>1.554259873683031</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-1.492288688885077</v>
+      </c>
+      <c r="C188">
+        <v>1.125140914316612</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.05644923326930901</v>
+      </c>
+      <c r="C189">
+        <v>-1.411543602728953</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1.143229025022189</v>
+      </c>
+      <c r="C190">
+        <v>0.8082607658841825</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>0.5840161549608264</v>
+      </c>
+      <c r="C191">
+        <v>0.2576527043634102</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.9626965525882532</v>
+      </c>
+      <c r="C192">
+        <v>0.7355494922603873</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.5148038453597753</v>
+      </c>
+      <c r="C193">
+        <v>1.965470053087909</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-1.529102043782049</v>
+      </c>
+      <c r="C194">
+        <v>0.6548726526708392</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.4139564898633235</v>
+      </c>
+      <c r="C195">
+        <v>1.723836284080174</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.1647878355392282</v>
+      </c>
+      <c r="C196">
+        <v>1.222333888243197</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.4293660275252174</v>
+      </c>
+      <c r="C197">
+        <v>0.9353330871609642</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.6406257889296367</v>
+      </c>
+      <c r="C198">
+        <v>-1.42392183738502</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-1.035001170529646</v>
+      </c>
+      <c r="C199">
+        <v>1.907273609182245</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-1.666036269117389</v>
+      </c>
+      <c r="C200">
+        <v>-0.9344042445820268</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.1507098769565483</v>
+      </c>
+      <c r="C201">
+        <v>-0.6510662709880564</v>
       </c>
     </row>
   </sheetData>
